--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_skill_effects.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_skill_effects.xlsx
@@ -10,7 +10,7 @@
     <sheet name="cfg_skill_effects" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_skill_effects!$A$4:$W$359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_skill_effects!$A$4:$W$361</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="576">
   <si>
     <t>id</t>
   </si>
@@ -1073,6 +1073,9 @@
     <t>玄月斩</t>
   </si>
   <si>
+    <t>143#144</t>
+  </si>
+  <si>
     <t>天雷闪施法特效</t>
   </si>
   <si>
@@ -1601,7 +1604,7 @@
     <t>玄月斩施法特效</t>
   </si>
   <si>
-    <t>138#143</t>
+    <t>138#143#144</t>
   </si>
   <si>
     <t>天雷轰顶施法特效</t>
@@ -1832,7 +1835,7 @@
     <t>星云火链</t>
   </si>
   <si>
-    <t>6000#6001#6002</t>
+    <t>1#1</t>
   </si>
   <si>
     <t>冲击波</t>
@@ -2022,6 +2025,12 @@
   </si>
   <si>
     <t>小挪移</t>
+  </si>
+  <si>
+    <t>星云召唤</t>
+  </si>
+  <si>
+    <t>惩戒屏障</t>
   </si>
 </sst>
 </file>
@@ -2034,7 +2043,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2061,6 +2070,12 @@
       <u/>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2518,31 +2533,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2551,119 +2563,122 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2688,6 +2703,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3232,7 +3250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:W359"/>
+  <dimension ref="A1:W361"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.57142857142857" style="1" customWidth="1"/>
@@ -3724,8 +3742,8 @@
       <c r="B13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="1">
-        <v>45</v>
+      <c r="C13" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="U13" s="1">
         <v>50008</v>
@@ -6639,8 +6657,8 @@
       <c r="B131" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C131" s="1">
-        <v>138</v>
+      <c r="C131" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="U131" s="1">
         <v>50051</v>
@@ -6651,7 +6669,7 @@
         <v>128</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C132" s="1">
         <v>102</v>
@@ -6663,7 +6681,7 @@
         <v>800</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="U132" s="1">
         <v>100065</v>
@@ -6674,7 +6692,7 @@
         <v>129</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C133" s="1">
         <v>104</v>
@@ -6688,7 +6706,7 @@
         <v>130</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M134" s="1">
         <v>1</v>
@@ -6708,7 +6726,7 @@
         <v>131</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C135" s="1">
         <v>107</v>
@@ -6722,10 +6740,10 @@
         <v>132</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E136" s="1">
         <v>200</v>
@@ -6742,7 +6760,7 @@
         <v>133</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C137" s="1">
         <v>120</v>
@@ -6762,7 +6780,7 @@
         <v>134</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C138" s="1">
         <v>119</v>
@@ -6776,7 +6794,7 @@
         <v>135</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C139" s="1">
         <v>122</v>
@@ -6788,13 +6806,13 @@
         <v>1</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q139" s="1">
         <v>1</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="S139" s="1">
         <v>1</v>
@@ -6808,10 +6826,10 @@
         <v>136</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="U140" s="1">
         <v>50040</v>
@@ -6822,7 +6840,7 @@
         <v>137</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F141" s="1">
         <v>1</v>
@@ -6845,7 +6863,7 @@
         <v>138</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F142" s="1">
         <v>1</v>
@@ -6868,7 +6886,7 @@
         <v>139</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F143" s="1">
         <v>1</v>
@@ -6891,7 +6909,7 @@
         <v>140</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F144" s="1">
         <v>1</v>
@@ -6914,7 +6932,7 @@
         <v>141</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F145" s="1">
         <v>1</v>
@@ -6937,7 +6955,7 @@
         <v>142</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F146" s="1">
         <v>1</v>
@@ -6960,7 +6978,7 @@
         <v>143</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F147" s="1">
         <v>1</v>
@@ -6972,7 +6990,7 @@
         <v>1000</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K147" s="1" t="s">
         <v>146</v>
@@ -6986,7 +7004,7 @@
         <v>144</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F148" s="1">
         <v>1</v>
@@ -6998,7 +7016,7 @@
         <v>1000</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K148" s="1" t="s">
         <v>146</v>
@@ -7012,7 +7030,7 @@
         <v>145</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F149" s="1">
         <v>1</v>
@@ -7024,7 +7042,7 @@
         <v>1000</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K149" s="1" t="s">
         <v>146</v>
@@ -7038,7 +7056,7 @@
         <v>146</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F150" s="1">
         <v>1</v>
@@ -7050,7 +7068,7 @@
         <v>1000</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="U150" s="1">
         <v>50035</v>
@@ -7061,7 +7079,7 @@
         <v>147</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>124</v>
@@ -7076,7 +7094,7 @@
         <v>1000</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U151" s="1">
         <v>50039</v>
@@ -7087,7 +7105,7 @@
         <v>148</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>124</v>
@@ -7102,7 +7120,7 @@
         <v>1000</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="U152" s="1">
         <v>50039</v>
@@ -7113,7 +7131,7 @@
         <v>149</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>124</v>
@@ -7128,7 +7146,7 @@
         <v>1000</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="U153" s="1">
         <v>50039</v>
@@ -7139,7 +7157,7 @@
         <v>150</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>124</v>
@@ -7154,7 +7172,7 @@
         <v>1000</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U154" s="1">
         <v>50039</v>
@@ -7165,7 +7183,7 @@
         <v>151</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>124</v>
@@ -7180,7 +7198,7 @@
         <v>1000</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U155" s="1">
         <v>50039</v>
@@ -7191,7 +7209,7 @@
         <v>152</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>124</v>
@@ -7206,7 +7224,7 @@
         <v>1000</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="U156" s="1">
         <v>50039</v>
@@ -7217,7 +7235,7 @@
         <v>153</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F157" s="1">
         <v>1</v>
@@ -7261,7 +7279,7 @@
         <v>154</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F158" s="1">
         <v>1</v>
@@ -7305,7 +7323,7 @@
         <v>155</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F159" s="1">
         <v>1</v>
@@ -7349,7 +7367,7 @@
         <v>156</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F160" s="1">
         <v>1</v>
@@ -7393,7 +7411,7 @@
         <v>157</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F161" s="1">
         <v>1</v>
@@ -7437,7 +7455,7 @@
         <v>158</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F162" s="1">
         <v>1</v>
@@ -7481,7 +7499,7 @@
         <v>159</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C163" s="1">
         <v>35</v>
@@ -7493,7 +7511,7 @@
         <v>1000</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K163" s="1" t="s">
         <v>157</v>
@@ -7507,7 +7525,7 @@
         <v>160</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C164" s="1">
         <v>35</v>
@@ -7519,7 +7537,7 @@
         <v>1000</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K164" s="1" t="s">
         <v>157</v>
@@ -7533,7 +7551,7 @@
         <v>161</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C165" s="1">
         <v>35</v>
@@ -7545,7 +7563,7 @@
         <v>1000</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K165" s="1" t="s">
         <v>157</v>
@@ -7559,7 +7577,7 @@
         <v>162</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C166" s="1">
         <v>35</v>
@@ -7571,7 +7589,7 @@
         <v>1000</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K166" s="1" t="s">
         <v>157</v>
@@ -7585,7 +7603,7 @@
         <v>163</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C167" s="1">
         <v>35</v>
@@ -7597,7 +7615,7 @@
         <v>1000</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K167" s="1" t="s">
         <v>157</v>
@@ -7611,7 +7629,7 @@
         <v>164</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C168" s="1">
         <v>35</v>
@@ -7623,7 +7641,7 @@
         <v>1000</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K168" s="1" t="s">
         <v>157</v>
@@ -7637,7 +7655,7 @@
         <v>165</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F169" s="1">
         <v>1</v>
@@ -7681,7 +7699,7 @@
         <v>166</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C170" s="1">
         <v>145</v>
@@ -7693,7 +7711,7 @@
         <v>1000</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M170" s="1">
         <v>1</v>
@@ -7725,7 +7743,7 @@
         <v>167</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C171" s="1">
         <v>145</v>
@@ -7737,7 +7755,7 @@
         <v>1000</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M171" s="1">
         <v>1</v>
@@ -7769,7 +7787,7 @@
         <v>168</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C172" s="1">
         <v>145</v>
@@ -7781,7 +7799,7 @@
         <v>1000</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M172" s="1">
         <v>1</v>
@@ -7813,7 +7831,7 @@
         <v>169</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C173" s="1">
         <v>145</v>
@@ -7825,7 +7843,7 @@
         <v>1000</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M173" s="1">
         <v>1</v>
@@ -7857,7 +7875,7 @@
         <v>170</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C174" s="1">
         <v>145</v>
@@ -7869,7 +7887,7 @@
         <v>1000</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M174" s="1">
         <v>1</v>
@@ -7901,7 +7919,7 @@
         <v>171</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C175" s="1">
         <v>145</v>
@@ -7913,7 +7931,7 @@
         <v>1000</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M175" s="1">
         <v>1</v>
@@ -7945,7 +7963,7 @@
         <v>172</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C176" s="1">
         <v>145</v>
@@ -7957,7 +7975,7 @@
         <v>1000</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M176" s="1">
         <v>1</v>
@@ -7989,7 +8007,7 @@
         <v>173</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C177" s="1">
         <v>145</v>
@@ -8001,7 +8019,7 @@
         <v>1000</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M177" s="1">
         <v>1</v>
@@ -8033,7 +8051,7 @@
         <v>174</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C178" s="1">
         <v>145</v>
@@ -8045,7 +8063,7 @@
         <v>1000</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M178" s="1">
         <v>1</v>
@@ -8077,7 +8095,7 @@
         <v>175</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C179" s="1">
         <v>145</v>
@@ -8089,7 +8107,7 @@
         <v>1000</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M179" s="1">
         <v>1</v>
@@ -8121,7 +8139,7 @@
         <v>176</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C180" s="1">
         <v>145</v>
@@ -8133,7 +8151,7 @@
         <v>1000</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M180" s="1">
         <v>1</v>
@@ -8165,7 +8183,7 @@
         <v>177</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C181" s="1">
         <v>145</v>
@@ -8177,7 +8195,7 @@
         <v>1000</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M181" s="1">
         <v>1</v>
@@ -8209,7 +8227,7 @@
         <v>178</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C182" s="1">
         <v>145</v>
@@ -8221,7 +8239,7 @@
         <v>1000</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M182" s="1">
         <v>1</v>
@@ -8253,7 +8271,7 @@
         <v>179</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C183" s="1">
         <v>145</v>
@@ -8265,7 +8283,7 @@
         <v>1000</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M183" s="1">
         <v>1</v>
@@ -8297,7 +8315,7 @@
         <v>180</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C184" s="1">
         <v>145</v>
@@ -8309,7 +8327,7 @@
         <v>1000</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M184" s="1">
         <v>1</v>
@@ -8341,7 +8359,7 @@
         <v>181</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C185" s="1">
         <v>145</v>
@@ -8353,7 +8371,7 @@
         <v>1000</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M185" s="1">
         <v>1</v>
@@ -8385,7 +8403,7 @@
         <v>182</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C186" s="1">
         <v>145</v>
@@ -8397,7 +8415,7 @@
         <v>1000</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M186" s="1">
         <v>1</v>
@@ -8429,7 +8447,7 @@
         <v>183</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C187" s="1">
         <v>145</v>
@@ -8441,7 +8459,7 @@
         <v>1000</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M187" s="1">
         <v>1</v>
@@ -8473,7 +8491,7 @@
         <v>184</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C188" s="1">
         <v>145</v>
@@ -8485,7 +8503,7 @@
         <v>1000</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M188" s="1">
         <v>1</v>
@@ -8517,7 +8535,7 @@
         <v>185</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C189" s="1">
         <v>126</v>
@@ -8529,7 +8547,7 @@
         <v>1000</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="U189" s="1">
         <v>50038</v>
@@ -8540,7 +8558,7 @@
         <v>186</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C190" s="1">
         <v>126</v>
@@ -8552,7 +8570,7 @@
         <v>1000</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K190" s="1" t="s">
         <v>157</v>
@@ -8566,7 +8584,7 @@
         <v>187</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C191" s="1">
         <v>126</v>
@@ -8578,7 +8596,7 @@
         <v>1000</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K191" s="1" t="s">
         <v>157</v>
@@ -8592,7 +8610,7 @@
         <v>188</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C192" s="1">
         <v>126</v>
@@ -8604,7 +8622,7 @@
         <v>1000</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K192" s="1" t="s">
         <v>157</v>
@@ -8618,7 +8636,7 @@
         <v>189</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C193" s="1">
         <v>126</v>
@@ -8630,7 +8648,7 @@
         <v>1000</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K193" s="1" t="s">
         <v>157</v>
@@ -8644,7 +8662,7 @@
         <v>190</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C194" s="1">
         <v>126</v>
@@ -8656,7 +8674,7 @@
         <v>1000</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K194" s="1" t="s">
         <v>157</v>
@@ -8670,7 +8688,7 @@
         <v>191</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C195" s="1">
         <v>126</v>
@@ -8682,7 +8700,7 @@
         <v>1000</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K195" s="1" t="s">
         <v>157</v>
@@ -8696,7 +8714,7 @@
         <v>192</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C196" s="1">
         <v>126</v>
@@ -8708,7 +8726,7 @@
         <v>1000</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K196" s="1" t="s">
         <v>157</v>
@@ -8722,7 +8740,7 @@
         <v>193</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C197" s="1">
         <v>126</v>
@@ -8734,7 +8752,7 @@
         <v>1000</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K197" s="1" t="s">
         <v>157</v>
@@ -8748,7 +8766,7 @@
         <v>194</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C198" s="1">
         <v>126</v>
@@ -8760,7 +8778,7 @@
         <v>1000</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K198" s="1" t="s">
         <v>157</v>
@@ -8774,7 +8792,7 @@
         <v>195</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C199" s="1">
         <v>126</v>
@@ -8786,7 +8804,7 @@
         <v>1000</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K199" s="1" t="s">
         <v>157</v>
@@ -8800,7 +8818,7 @@
         <v>196</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C200" s="1">
         <v>126</v>
@@ -8812,7 +8830,7 @@
         <v>1000</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U200" s="1">
         <v>50038</v>
@@ -8823,7 +8841,7 @@
         <v>197</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C201" s="1">
         <v>126</v>
@@ -8835,7 +8853,7 @@
         <v>1000</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U201" s="1">
         <v>50038</v>
@@ -8846,7 +8864,7 @@
         <v>198</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C202" s="1">
         <v>126</v>
@@ -8858,7 +8876,7 @@
         <v>1000</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="U202" s="1">
         <v>50038</v>
@@ -8869,7 +8887,7 @@
         <v>199</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C203" s="1">
         <v>126</v>
@@ -8881,7 +8899,7 @@
         <v>1000</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="U203" s="1">
         <v>50038</v>
@@ -8892,7 +8910,7 @@
         <v>200</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C204" s="1">
         <v>126</v>
@@ -8904,7 +8922,7 @@
         <v>1000</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="U204" s="1">
         <v>50038</v>
@@ -8915,7 +8933,7 @@
         <v>201</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C205" s="1">
         <v>126</v>
@@ -8927,7 +8945,7 @@
         <v>1000</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="U205" s="1">
         <v>50038</v>
@@ -8938,7 +8956,7 @@
         <v>202</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C206" s="1">
         <v>126</v>
@@ -8950,7 +8968,7 @@
         <v>1000</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U206" s="1">
         <v>50038</v>
@@ -8961,7 +8979,7 @@
         <v>203</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C207" s="1">
         <v>126</v>
@@ -8973,7 +8991,7 @@
         <v>1000</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="U207" s="1">
         <v>50038</v>
@@ -8984,10 +9002,10 @@
         <v>204</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F208" s="1">
         <v>1</v>
@@ -8996,10 +9014,10 @@
         <v>1000</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U208" s="1">
         <v>50039</v>
@@ -9010,10 +9028,10 @@
         <v>205</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F209" s="1">
         <v>1</v>
@@ -9025,7 +9043,7 @@
         <v>219</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U209" s="1">
         <v>50039</v>
@@ -9036,10 +9054,10 @@
         <v>206</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F210" s="1">
         <v>1</v>
@@ -9051,7 +9069,7 @@
         <v>222</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U210" s="1">
         <v>50039</v>
@@ -9062,10 +9080,10 @@
         <v>207</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F211" s="1">
         <v>1</v>
@@ -9077,7 +9095,7 @@
         <v>224</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U211" s="1">
         <v>50039</v>
@@ -9088,10 +9106,10 @@
         <v>208</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F212" s="1">
         <v>1</v>
@@ -9103,7 +9121,7 @@
         <v>254</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U212" s="1">
         <v>50039</v>
@@ -9114,10 +9132,10 @@
         <v>209</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F213" s="1">
         <v>1</v>
@@ -9126,10 +9144,10 @@
         <v>1000</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U213" s="1">
         <v>50039</v>
@@ -9140,10 +9158,10 @@
         <v>210</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F214" s="1">
         <v>1</v>
@@ -9152,10 +9170,10 @@
         <v>1000</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U214" s="1">
         <v>50039</v>
@@ -9166,10 +9184,10 @@
         <v>211</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F215" s="1">
         <v>1</v>
@@ -9178,10 +9196,10 @@
         <v>1000</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U215" s="1">
         <v>50039</v>
@@ -9192,10 +9210,10 @@
         <v>212</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F216" s="1">
         <v>1</v>
@@ -9204,10 +9222,10 @@
         <v>1000</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U216" s="1">
         <v>50039</v>
@@ -9218,10 +9236,10 @@
         <v>213</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F217" s="1">
         <v>1</v>
@@ -9230,10 +9248,10 @@
         <v>1000</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U217" s="1">
         <v>50039</v>
@@ -9244,10 +9262,10 @@
         <v>214</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F218" s="1">
         <v>1</v>
@@ -9256,10 +9274,10 @@
         <v>1000</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J218" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U218" s="1">
         <v>50039</v>
@@ -9270,10 +9288,10 @@
         <v>215</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F219" s="1">
         <v>1</v>
@@ -9282,10 +9300,10 @@
         <v>1000</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U219" s="1">
         <v>50039</v>
@@ -9296,10 +9314,10 @@
         <v>216</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F220" s="1">
         <v>1</v>
@@ -9308,10 +9326,10 @@
         <v>1000</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U220" s="1">
         <v>50039</v>
@@ -9322,10 +9340,10 @@
         <v>217</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F221" s="1">
         <v>1</v>
@@ -9334,10 +9352,10 @@
         <v>1000</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U221" s="1">
         <v>50039</v>
@@ -9348,10 +9366,10 @@
         <v>218</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F222" s="1">
         <v>1</v>
@@ -9360,10 +9378,10 @@
         <v>1000</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U222" s="1">
         <v>50039</v>
@@ -9374,10 +9392,10 @@
         <v>219</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F223" s="1">
         <v>1</v>
@@ -9386,10 +9404,10 @@
         <v>1000</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U223" s="1">
         <v>50039</v>
@@ -9400,10 +9418,10 @@
         <v>220</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F224" s="1">
         <v>1</v>
@@ -9412,10 +9430,10 @@
         <v>1000</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U224" s="1">
         <v>50039</v>
@@ -9426,10 +9444,10 @@
         <v>221</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F225" s="1">
         <v>1</v>
@@ -9438,10 +9456,10 @@
         <v>1000</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U225" s="1">
         <v>50039</v>
@@ -9452,10 +9470,10 @@
         <v>222</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F226" s="1">
         <v>1</v>
@@ -9464,10 +9482,10 @@
         <v>1000</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U226" s="1">
         <v>50039</v>
@@ -9478,10 +9496,10 @@
         <v>223</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F227" s="1">
         <v>1</v>
@@ -9490,10 +9508,10 @@
         <v>1000</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U227" s="1">
         <v>50039</v>
@@ -9504,10 +9522,10 @@
         <v>224</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="U228" s="1">
         <v>50011</v>
@@ -9518,7 +9536,7 @@
         <v>225</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C229" s="1">
         <v>130</v>
@@ -9544,7 +9562,7 @@
         <v>72</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>74</v>
@@ -9558,10 +9576,10 @@
         <v>227</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M231" s="1">
         <v>1</v>
@@ -9587,13 +9605,13 @@
         <v>228</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M232" s="1">
         <v>1</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P232" s="1" t="s">
         <v>106</v>
@@ -9610,7 +9628,7 @@
         <v>229</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M233" s="1">
         <v>1</v>
@@ -9630,10 +9648,10 @@
         <v>230</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="U234" s="1">
         <v>50052</v>
@@ -9644,7 +9662,7 @@
         <v>231</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C235" s="1">
         <v>139</v>
@@ -9658,10 +9676,10 @@
         <v>232</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="U236" s="1">
         <v>50051</v>
@@ -9672,7 +9690,7 @@
         <v>233</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C237" s="1">
         <v>126</v>
@@ -9684,7 +9702,7 @@
         <v>1000</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U237" s="1">
         <v>50038</v>
@@ -9695,7 +9713,7 @@
         <v>234</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C238" s="1">
         <v>145</v>
@@ -9707,7 +9725,7 @@
         <v>1000</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M238" s="1">
         <v>1</v>
@@ -9739,7 +9757,7 @@
         <v>1001</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F239" s="1">
         <v>1</v>
@@ -9768,7 +9786,7 @@
         <v>1002</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F240" s="1">
         <v>1</v>
@@ -9797,7 +9815,7 @@
         <v>1004</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C241" s="1">
         <v>1004</v>
@@ -9820,7 +9838,7 @@
         <v>1005</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F242" s="1">
         <v>1</v>
@@ -9840,7 +9858,7 @@
         <v>1006</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F243" s="1">
         <v>1</v>
@@ -9857,7 +9875,7 @@
         <v>1007</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M244" s="1">
         <v>1</v>
@@ -9891,7 +9909,7 @@
         <v>1010</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H246" s="1">
         <v>1000</v>
@@ -9908,7 +9926,7 @@
         <v>1011</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C247" s="1">
         <v>1011</v>
@@ -9922,7 +9940,7 @@
         <v>1012</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C248" s="1">
         <v>2011</v>
@@ -9948,7 +9966,7 @@
         <v>1014</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C249" s="1">
         <v>1014</v>
@@ -9962,7 +9980,7 @@
         <v>1015</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C250" s="1">
         <v>1015</v>
@@ -9976,7 +9994,7 @@
         <v>1016</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C251" s="1">
         <v>1016</v>
@@ -9990,7 +10008,7 @@
         <v>1017</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F252" s="1">
         <v>1</v>
@@ -10007,7 +10025,7 @@
         <v>1018</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C253" s="1">
         <v>2024</v>
@@ -10021,7 +10039,7 @@
         <v>1021</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F254" s="1">
         <v>1</v>
@@ -10041,7 +10059,7 @@
         <v>1022</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>73</v>
@@ -10055,7 +10073,7 @@
         <v>1023</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M256" s="1">
         <v>1</v>
@@ -10078,7 +10096,7 @@
         <v>1024</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M257" s="1">
         <v>1</v>
@@ -10101,7 +10119,7 @@
         <v>1025</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C258" s="1">
         <v>1022</v>
@@ -10115,7 +10133,7 @@
         <v>1026</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C259" s="1">
         <v>1023</v>
@@ -10129,7 +10147,7 @@
         <v>1027</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C260" s="1">
         <v>1024</v>
@@ -10167,7 +10185,7 @@
         <v>1028</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M261" s="1">
         <v>1</v>
@@ -10190,7 +10208,7 @@
         <v>1029</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C262" s="1">
         <v>1028</v>
@@ -10204,7 +10222,7 @@
         <v>2001</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C263" s="1">
         <v>2001</v>
@@ -10246,7 +10264,7 @@
         <v>2004</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F266" s="1">
         <v>1</v>
@@ -10266,7 +10284,7 @@
         <v>2005</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C267" s="1">
         <v>2006</v>
@@ -10286,7 +10304,7 @@
         <v>2006</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C268" s="1">
         <v>2007</v>
@@ -10309,7 +10327,7 @@
         <v>1000</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="270" spans="1:17">
@@ -10317,7 +10335,7 @@
         <v>2008</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C270" s="1">
         <v>2009</v>
@@ -10342,7 +10360,7 @@
         <v>2010</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C272" s="1">
         <v>2011</v>
@@ -10362,7 +10380,7 @@
         <v>2011</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C273" s="1">
         <v>2012</v>
@@ -10373,7 +10391,7 @@
         <v>2012</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C274" s="1">
         <v>2013</v>
@@ -10387,7 +10405,7 @@
         <v>2013</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C275" s="1">
         <v>2014</v>
@@ -10398,7 +10416,7 @@
         <v>2014</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C276" s="1">
         <v>2015</v>
@@ -10418,7 +10436,7 @@
         <v>2015</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C277" s="1">
         <v>2016</v>
@@ -10429,7 +10447,7 @@
         <v>2016</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C278" s="1">
         <v>2017</v>
@@ -10449,7 +10467,7 @@
         <v>2017</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C279" s="1">
         <v>2018</v>
@@ -10463,7 +10481,7 @@
         <v>2018</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C280" s="1">
         <v>2020</v>
@@ -10474,7 +10492,7 @@
         <v>2019</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C281" s="1">
         <v>2021</v>
@@ -10494,7 +10512,7 @@
         <v>2020</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C282" s="1">
         <v>2022</v>
@@ -10514,7 +10532,7 @@
         <v>2021</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C283" s="1">
         <v>2023</v>
@@ -10534,7 +10552,7 @@
         <v>2022</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C284" s="1">
         <v>2024</v>
@@ -10545,7 +10563,7 @@
         <v>2023</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C285" s="1">
         <v>2025</v>
@@ -10565,10 +10583,10 @@
         <v>2024</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M286" s="1">
         <v>1</v>
@@ -10585,7 +10603,7 @@
         <v>2025</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="288" spans="1:17">
@@ -10593,7 +10611,7 @@
         <v>2026</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>97</v>
@@ -10610,7 +10628,7 @@
         <v>2027</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C289" s="1">
         <v>19</v>
@@ -10630,7 +10648,7 @@
         <v>2028</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="291" spans="1:20">
@@ -10638,10 +10656,10 @@
         <v>2029</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M291" s="1">
         <v>1</v>
@@ -10652,7 +10670,7 @@
         <v>2030</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F292" s="1">
         <v>1</v>
@@ -10672,7 +10690,7 @@
         <v>3001</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C293" s="1">
         <v>3001</v>
@@ -10686,7 +10704,7 @@
         <v>3002</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C294" s="1">
         <v>3002</v>
@@ -10700,7 +10718,7 @@
         <v>3003</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C295" s="1">
         <v>3003</v>
@@ -10714,7 +10732,7 @@
         <v>4000</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C296" s="1">
         <v>4000</v>
@@ -10728,7 +10746,7 @@
         <v>4010</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C297" s="1">
         <v>4010</v>
@@ -10742,7 +10760,7 @@
         <v>4020</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C298" s="1">
         <v>4020</v>
@@ -10753,7 +10771,7 @@
         <v>4030</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C299" s="1">
         <v>4030</v>
@@ -10764,7 +10782,7 @@
         <v>4040</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C300" s="1">
         <v>4040</v>
@@ -10784,7 +10802,7 @@
         <v>4050</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C301" s="1">
         <v>4050</v>
@@ -10816,7 +10834,7 @@
         <v>4060</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C302" s="1">
         <v>4060</v>
@@ -10827,7 +10845,7 @@
         <v>4070</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C303" s="1">
         <v>4070</v>
@@ -10839,7 +10857,7 @@
         <v>1000</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="304" spans="1:20">
@@ -10847,7 +10865,7 @@
         <v>4080</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C304" s="1">
         <v>4080</v>
@@ -10862,12 +10880,12 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="305" spans="1:20">
+    <row r="305" spans="1:23">
       <c r="A305" s="1">
         <v>4090</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C305" s="1">
         <v>4090</v>
@@ -10876,12 +10894,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:20">
+    <row r="306" spans="1:23">
       <c r="A306" s="1">
         <v>4100</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C306" s="1">
         <v>4100</v>
@@ -10896,69 +10914,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:20">
+    <row r="307" spans="1:23">
       <c r="A307" s="1">
         <v>4110</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C307" s="1">
         <v>4110</v>
       </c>
     </row>
-    <row r="308" spans="1:20">
+    <row r="308" spans="1:23">
       <c r="A308" s="1">
         <v>4112</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C308" s="1">
         <v>4112</v>
       </c>
     </row>
-    <row r="309" spans="1:20">
+    <row r="309" customFormat="1" spans="1:23">
       <c r="A309" s="1">
         <v>6000</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C309" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="E309" s="1">
-        <v>300</v>
-      </c>
-      <c r="F309" s="1">
-        <v>1</v>
-      </c>
-      <c r="M309" s="1">
-        <v>1</v>
-      </c>
-      <c r="N309" s="1">
-        <v>1</v>
-      </c>
-      <c r="O309" s="1">
+      <c r="C309" s="1">
         <v>6000</v>
       </c>
-      <c r="P309" s="1">
-        <v>300</v>
-      </c>
-      <c r="R309" s="1">
-        <v>6000</v>
-      </c>
-      <c r="T309" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="310" spans="1:20">
+      <c r="D309" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="E309" s="1"/>
+      <c r="F309" s="1"/>
+      <c r="G309" s="1"/>
+      <c r="H309" s="1"/>
+      <c r="I309" s="1"/>
+      <c r="J309" s="1"/>
+      <c r="K309" s="1"/>
+      <c r="L309" s="1"/>
+      <c r="M309" s="1"/>
+      <c r="N309" s="1"/>
+      <c r="O309" s="1"/>
+      <c r="P309" s="1"/>
+      <c r="Q309" s="1"/>
+      <c r="R309" s="1"/>
+      <c r="S309" s="1"/>
+      <c r="T309" s="1"/>
+      <c r="U309" s="1"/>
+      <c r="V309" s="1"/>
+      <c r="W309" s="1"/>
+    </row>
+    <row r="310" spans="1:23">
       <c r="A310" s="1">
         <v>6001</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C310" s="1">
         <v>6003</v>
@@ -10966,25 +10982,22 @@
       <c r="E310" s="1">
         <v>300</v>
       </c>
-      <c r="F310" s="1">
-        <v>1</v>
-      </c>
       <c r="H310" s="1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="311" spans="1:20">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="311" spans="1:23">
       <c r="A311" s="1">
         <v>6002</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E311" s="1">
         <v>300</v>
@@ -11014,42 +11027,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:20">
+    <row r="312" spans="1:23">
       <c r="A312" s="1">
-        <v>6003</v>
+        <v>1014010</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="313" spans="1:20">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="313" spans="1:23">
       <c r="A313" s="1">
         <v>6004</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="314" spans="1:20">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="314" spans="1:23">
       <c r="A314" s="1">
         <v>6005</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="315" spans="1:20">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="315" spans="1:23">
       <c r="A315" s="1">
         <v>6006</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C315" s="1">
         <v>6010</v>
@@ -11064,26 +11077,26 @@
         <v>800</v>
       </c>
     </row>
-    <row r="316" spans="1:20">
+    <row r="316" spans="1:23">
       <c r="A316" s="1">
         <v>6007</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="317" spans="1:20">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="317" spans="1:23">
       <c r="A317" s="1">
         <v>6008</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>523</v>
+      <c r="B317" s="2" t="s">
+        <v>524</v>
       </c>
       <c r="C317" s="1">
         <v>6015</v>
@@ -11092,7 +11105,7 @@
         <v>1</v>
       </c>
       <c r="H317" s="1">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="I317" s="1">
         <v>6015</v>
@@ -11101,37 +11114,37 @@
         <v>400</v>
       </c>
     </row>
-    <row r="318" spans="1:20">
+    <row r="318" spans="1:23">
       <c r="A318" s="1">
         <v>6009</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="319" spans="1:20">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="319" spans="1:23">
       <c r="A319" s="1">
         <v>6010</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="320" spans="1:20">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="320" spans="1:23">
       <c r="A320" s="1">
         <v>6011</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C320" s="1">
         <v>6023</v>
@@ -11142,7 +11155,7 @@
         <v>6012</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C321" s="1">
         <v>6050</v>
@@ -11153,7 +11166,7 @@
         <v>6013</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C322" s="1">
         <v>6060</v>
@@ -11167,7 +11180,7 @@
         <v>6014</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C323" s="1">
         <v>6070</v>
@@ -11181,10 +11194,10 @@
         <v>6015</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="325" spans="1:23">
@@ -11192,10 +11205,10 @@
         <v>6016</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="326" spans="1:23">
@@ -11203,10 +11216,10 @@
         <v>6017</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="327" spans="1:23">
@@ -11214,7 +11227,7 @@
         <v>6018</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C327" s="1">
         <v>6035</v>
@@ -11228,7 +11241,7 @@
         <v>23501</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C328" s="1">
         <v>6101</v>
@@ -11250,7 +11263,7 @@
         <v>23502</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C329" s="1">
         <v>6102</v>
@@ -11264,7 +11277,7 @@
         <v>23503</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C330" s="1">
         <v>6103</v>
@@ -11278,7 +11291,7 @@
         <v>23504</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C331" s="1">
         <v>6104</v>
@@ -11292,7 +11305,7 @@
         <v>23505</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C332" s="1">
         <v>6105</v>
@@ -11306,7 +11319,7 @@
         <v>23506</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C333" s="1">
         <v>6106</v>
@@ -11320,7 +11333,7 @@
         <v>23507</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C334" s="1">
         <v>6107</v>
@@ -11334,7 +11347,7 @@
         <v>2000062</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C335" s="1">
         <v>2000062</v>
@@ -11365,7 +11378,7 @@
         <v>2040011</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C336" s="1">
         <v>2040011</v>
@@ -11382,7 +11395,7 @@
         <v>2040021</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C337" s="1">
         <v>2040021</v>
@@ -11399,7 +11412,7 @@
         <v>2040031</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C338" s="1"/>
       <c r="D338" s="1"/>
@@ -11423,7 +11436,7 @@
         <v>2040041</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C339" s="1">
         <v>2040041</v>
@@ -11440,7 +11453,7 @@
         <v>2040051</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C340" s="1">
         <v>2040051</v>
@@ -11457,7 +11470,7 @@
         <v>2040061</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C341" s="1"/>
       <c r="D341" s="1"/>
@@ -11478,7 +11491,7 @@
         <v>10040231</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C342" s="1">
         <v>10040231</v>
@@ -11492,7 +11505,7 @@
         <v>1016006</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C343" s="4"/>
       <c r="M343" s="1">
@@ -11525,7 +11538,7 @@
         <v>1016013</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C344" s="4"/>
       <c r="M344" s="1">
@@ -11558,7 +11571,7 @@
         <v>1016011</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C345" s="1">
         <v>60000009</v>
@@ -11572,7 +11585,7 @@
         <v>1016007</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C346" s="4">
         <v>60000002</v>
@@ -11587,10 +11600,10 @@
         <v>1016010</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>71</v>
@@ -11604,7 +11617,7 @@
         <v>1016005</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C348" s="4"/>
       <c r="F348" s="1">
@@ -11625,7 +11638,7 @@
         <v>1016009</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C349" s="4">
         <v>60000006</v>
@@ -11639,7 +11652,7 @@
         <v>1016014</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C350" s="1">
         <v>60000017</v>
@@ -11665,7 +11678,7 @@
         <v>1016008</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C351" s="1">
         <v>60000004</v>
@@ -11691,7 +11704,7 @@
         <v>1016012</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C352" s="1">
         <v>60000010</v>
@@ -11705,7 +11718,7 @@
         <v>1016016</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C353" s="4">
         <v>60000019</v>
@@ -11719,7 +11732,7 @@
         <v>1016017</v>
       </c>
       <c r="B354" s="8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C354" s="1">
         <v>30</v>
@@ -11752,7 +11765,7 @@
         <v>1007001</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M355" s="1">
         <v>1</v>
@@ -11781,7 +11794,7 @@
         <v>1007002</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M356" s="1">
         <v>1</v>
@@ -11801,7 +11814,7 @@
         <v>1007003</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F357" s="1">
         <v>1</v>
@@ -11824,7 +11837,7 @@
         <v>10070031</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C358" s="1">
         <v>10070032</v>
@@ -11841,7 +11854,7 @@
         <v>1200018</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>100</v>
@@ -11868,27 +11881,103 @@
         <v>50018</v>
       </c>
     </row>
+    <row r="360" customFormat="1" ht="16.5" spans="1:21">
+      <c r="A360" s="6">
+        <v>1005007</v>
+      </c>
+      <c r="B360" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D360" s="1">
+        <v>1</v>
+      </c>
+      <c r="E360" s="1"/>
+      <c r="F360" s="1"/>
+      <c r="G360" s="1"/>
+      <c r="H360" s="1"/>
+      <c r="I360" s="1"/>
+      <c r="J360" s="1"/>
+      <c r="K360" s="1"/>
+      <c r="L360" s="1"/>
+      <c r="M360" s="1"/>
+      <c r="N360" s="1"/>
+      <c r="O360" s="1"/>
+      <c r="P360" s="1"/>
+      <c r="Q360" s="1"/>
+      <c r="R360" s="1"/>
+      <c r="S360" s="1"/>
+      <c r="T360" s="1"/>
+      <c r="U360" s="1">
+        <v>50012</v>
+      </c>
+    </row>
+    <row r="361" customFormat="1" ht="16.5" spans="1:21">
+      <c r="A361" s="1">
+        <v>1007004</v>
+      </c>
+      <c r="B361" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="C361" s="4">
+        <v>10070041</v>
+      </c>
+      <c r="D361" s="1">
+        <v>1</v>
+      </c>
+      <c r="E361" s="1"/>
+      <c r="F361" s="1"/>
+      <c r="G361" s="1"/>
+      <c r="H361" s="1"/>
+      <c r="I361" s="1"/>
+      <c r="J361" s="1"/>
+      <c r="K361" s="1"/>
+      <c r="L361" s="1"/>
+      <c r="M361" s="1"/>
+      <c r="N361" s="1"/>
+      <c r="O361" s="1"/>
+      <c r="P361" s="1"/>
+      <c r="Q361" s="1"/>
+      <c r="R361" s="1"/>
+      <c r="S361" s="1"/>
+      <c r="T361" s="1"/>
+      <c r="U361" s="1">
+        <v>50012</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:W359" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:W361" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A348">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A356">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A357">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A358">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A359">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A360">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A361">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A356">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A357">
+  <conditionalFormatting sqref="C361">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A358">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A359">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A355 A360:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="A1:A355 A362:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_skill_effects.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_skill_effects.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="576">
   <si>
     <t>id</t>
   </si>
@@ -420,6 +420,66 @@
 例如: 0#1#2</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>填写</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>cfg_audio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>表对应的音效</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">id
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>空为不播放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>释放时，播放音效</t>
+    </r>
+  </si>
+  <si>
     <t>填写cfg_audio表对应的音效id
 空为不播放
 释放时，播放音效</t>
@@ -1833,9 +1893,6 @@
   </si>
   <si>
     <t>星云火链</t>
-  </si>
-  <si>
-    <t>1#1</t>
   </si>
   <si>
     <t>冲击波</t>
@@ -3408,85 +3465,85 @@
       <c r="T2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="3" t="s">
         <v>39</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -3494,70 +3551,70 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -3565,7 +3622,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -3573,13 +3630,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M6" s="1">
         <v>1</v>
@@ -3588,13 +3645,13 @@
         <v>1</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R6" s="1">
         <v>3</v>
@@ -3614,13 +3671,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U7" s="1">
         <v>50014</v>
@@ -3637,7 +3694,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="1">
         <v>9</v>
@@ -3672,10 +3729,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M9" s="1">
         <v>1</v>
@@ -3695,10 +3752,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U10" s="1">
         <v>50011</v>
@@ -3709,10 +3766,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -3726,10 +3783,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U12" s="1">
         <v>50028</v>
@@ -3740,10 +3797,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="U13" s="1">
         <v>50008</v>
@@ -3754,10 +3811,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U14" s="1">
         <v>50008</v>
@@ -3768,7 +3825,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -3800,7 +3857,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
@@ -3820,7 +3877,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M17" s="1">
         <v>1</v>
@@ -3849,7 +3906,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
@@ -3869,7 +3926,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
@@ -3889,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -3909,7 +3966,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" s="1">
         <v>20</v>
@@ -3932,10 +3989,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M22" s="1">
         <v>1</v>
@@ -3961,7 +4018,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E23" s="1">
         <v>1000</v>
@@ -3984,10 +4041,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E24" s="1">
         <v>800</v>
@@ -4004,7 +4061,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M25" s="1">
         <v>1</v>
@@ -4027,16 +4084,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="U26" s="1">
         <v>50018</v>
@@ -4047,7 +4104,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E27" s="1">
         <v>200</v>
@@ -4070,7 +4127,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C28" s="1">
         <v>29</v>
@@ -4084,7 +4141,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C29" s="1">
         <v>30</v>
@@ -4101,7 +4158,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M30" s="1">
         <v>1</v>
@@ -4110,7 +4167,7 @@
         <v>31</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q30" s="1">
         <v>2</v>
@@ -4127,7 +4184,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M31" s="1">
         <v>1</v>
@@ -4150,7 +4207,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C32" s="1">
         <v>35</v>
@@ -4162,7 +4219,7 @@
         <v>1000</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U32" s="1">
         <v>50038</v>
@@ -4173,7 +4230,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F33" s="1">
         <v>1</v>
@@ -4185,7 +4242,7 @@
         <v>1000</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="U33" s="1">
         <v>50036</v>
@@ -4196,7 +4253,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M34" s="1">
         <v>1</v>
@@ -4213,7 +4270,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M35" s="1">
         <v>1</v>
@@ -4230,7 +4287,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M36" s="1">
         <v>1</v>
@@ -4247,7 +4304,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M37" s="1">
         <v>1</v>
@@ -4264,7 +4321,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M38" s="1">
         <v>1</v>
@@ -4281,7 +4338,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M39" s="1">
         <v>1</v>
@@ -4298,7 +4355,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M40" s="1">
         <v>1</v>
@@ -4315,7 +4372,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M41" s="1">
         <v>1</v>
@@ -4347,7 +4404,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M42" s="1">
         <v>1</v>
@@ -4379,7 +4436,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M43" s="1">
         <v>1</v>
@@ -4411,7 +4468,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F44" s="1">
         <v>1</v>
@@ -4428,10 +4485,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
@@ -4443,7 +4500,7 @@
         <v>1000</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -4451,7 +4508,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C46" s="1">
         <v>45</v>
@@ -4462,13 +4519,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -4476,7 +4533,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M48" s="1">
         <v>1</v>
@@ -4508,7 +4565,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
@@ -4525,7 +4582,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F50" s="1">
         <v>1</v>
@@ -4545,7 +4602,7 @@
         <v>47</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -4565,7 +4622,7 @@
         <v>48</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F52" s="1">
         <v>1</v>
@@ -4582,7 +4639,7 @@
         <v>49</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F53" s="1">
         <v>1</v>
@@ -4608,7 +4665,7 @@
         <v>50</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C54" s="1">
         <v>25</v>
@@ -4625,7 +4682,7 @@
         <v>51</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C55" s="1">
         <v>7</v>
@@ -4636,10 +4693,10 @@
         <v>52</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:21">
@@ -4647,10 +4704,10 @@
         <v>53</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:21">
@@ -4658,10 +4715,10 @@
         <v>54</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:21">
@@ -4669,7 +4726,7 @@
         <v>55</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C59" s="1">
         <v>35</v>
@@ -4684,10 +4741,10 @@
         <v>1000</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
@@ -4704,7 +4761,7 @@
         <v>56</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F60" s="1">
         <v>1</v>
@@ -4733,7 +4790,7 @@
         <v>57</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
@@ -4750,7 +4807,7 @@
         <v>58</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -4770,7 +4827,7 @@
         <v>59</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1">
         <v>71</v>
@@ -4787,7 +4844,7 @@
         <v>60</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F64" s="1">
         <v>1</v>
@@ -4799,10 +4856,10 @@
         <v>1000</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U64" s="1">
         <v>50036</v>
@@ -4813,22 +4870,22 @@
         <v>61</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F65" s="1">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K65" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="F65" s="1">
-        <v>1</v>
-      </c>
-      <c r="G65" s="1">
-        <v>1</v>
-      </c>
-      <c r="H65" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="U65" s="1">
         <v>50036</v>
@@ -4839,7 +4896,7 @@
         <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F66" s="1">
         <v>1</v>
@@ -4851,10 +4908,10 @@
         <v>1000</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U66" s="1">
         <v>50036</v>
@@ -4865,7 +4922,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F67" s="1">
         <v>1</v>
@@ -4877,10 +4934,10 @@
         <v>1000</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U67" s="1">
         <v>50036</v>
@@ -4891,7 +4948,7 @@
         <v>64</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F68" s="1">
         <v>1</v>
@@ -4903,10 +4960,10 @@
         <v>1000</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U68" s="1">
         <v>50036</v>
@@ -4917,7 +4974,7 @@
         <v>65</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1">
         <v>35</v>
@@ -4929,10 +4986,10 @@
         <v>1000</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U69" s="1">
         <v>50036</v>
@@ -4943,7 +5000,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C70" s="1">
         <v>35</v>
@@ -4955,10 +5012,10 @@
         <v>1000</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U70" s="1">
         <v>50036</v>
@@ -4969,7 +5026,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C71" s="1">
         <v>35</v>
@@ -4981,10 +5038,10 @@
         <v>1000</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U71" s="1">
         <v>50036</v>
@@ -4995,7 +5052,7 @@
         <v>68</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F72" s="1">
         <v>1</v>
@@ -5039,7 +5096,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F73" s="1">
         <v>1</v>
@@ -5083,7 +5140,7 @@
         <v>70</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F74" s="1">
         <v>1</v>
@@ -5127,7 +5184,7 @@
         <v>71</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F75" s="1">
         <v>1</v>
@@ -5168,7 +5225,7 @@
         <v>72</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F76" s="1">
         <v>1</v>
@@ -5209,7 +5266,7 @@
         <v>73</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F77" s="1">
         <v>1</v>
@@ -5250,7 +5307,7 @@
         <v>74</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F78" s="1">
         <v>1</v>
@@ -5291,7 +5348,7 @@
         <v>75</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F79" s="1">
         <v>1</v>
@@ -5332,7 +5389,7 @@
         <v>76</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F80" s="1">
         <v>1</v>
@@ -5373,7 +5430,7 @@
         <v>77</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F81" s="1">
         <v>1</v>
@@ -5414,7 +5471,7 @@
         <v>78</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F82" s="1">
         <v>1</v>
@@ -5455,7 +5512,7 @@
         <v>79</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F83" s="1">
         <v>1</v>
@@ -5496,7 +5553,7 @@
         <v>80</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F84" s="1">
         <v>1</v>
@@ -5508,10 +5565,10 @@
         <v>1000</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U84" s="1">
         <v>50036</v>
@@ -5522,7 +5579,7 @@
         <v>81</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C85" s="1">
         <v>35</v>
@@ -5534,10 +5591,10 @@
         <v>1000</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U85" s="1">
         <v>50036</v>
@@ -5548,7 +5605,7 @@
         <v>82</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F86" s="1">
         <v>1</v>
@@ -5592,7 +5649,7 @@
         <v>83</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F87" s="1">
         <v>1</v>
@@ -5615,7 +5672,7 @@
         <v>84</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F88" s="1">
         <v>1</v>
@@ -5638,7 +5695,7 @@
         <v>85</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F89" s="1">
         <v>1</v>
@@ -5661,7 +5718,7 @@
         <v>86</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C90" s="1">
         <v>35</v>
@@ -5673,7 +5730,7 @@
         <v>1000</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="U90" s="1">
         <v>50036</v>
@@ -5684,7 +5741,7 @@
         <v>87</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C91" s="1">
         <v>35</v>
@@ -5696,7 +5753,7 @@
         <v>1000</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="U91" s="1">
         <v>50036</v>
@@ -5707,7 +5764,7 @@
         <v>88</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C92" s="1">
         <v>35</v>
@@ -5719,7 +5776,7 @@
         <v>1000</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="U92" s="1">
         <v>50036</v>
@@ -5730,7 +5787,7 @@
         <v>89</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C93" s="1">
         <v>35</v>
@@ -5742,7 +5799,7 @@
         <v>1000</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="U93" s="1">
         <v>50036</v>
@@ -5753,7 +5810,7 @@
         <v>90</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C94" s="1">
         <v>35</v>
@@ -5765,7 +5822,7 @@
         <v>1000</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U94" s="1">
         <v>50036</v>
@@ -5776,7 +5833,7 @@
         <v>91</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C95" s="1">
         <v>35</v>
@@ -5788,7 +5845,7 @@
         <v>1000</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="U95" s="1">
         <v>50036</v>
@@ -5799,7 +5856,7 @@
         <v>92</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C96" s="1">
         <v>35</v>
@@ -5811,7 +5868,7 @@
         <v>1000</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U96" s="1">
         <v>50036</v>
@@ -5822,7 +5879,7 @@
         <v>93</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C97" s="1">
         <v>35</v>
@@ -5834,7 +5891,7 @@
         <v>1000</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U97" s="1">
         <v>50036</v>
@@ -5845,7 +5902,7 @@
         <v>94</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C98" s="1">
         <v>35</v>
@@ -5857,7 +5914,7 @@
         <v>1000</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="U98" s="1">
         <v>50036</v>
@@ -5868,7 +5925,7 @@
         <v>95</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F99" s="1">
         <v>1</v>
@@ -5880,7 +5937,7 @@
         <v>1000</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U99" s="1">
         <v>50036</v>
@@ -5891,7 +5948,7 @@
         <v>96</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F100" s="1">
         <v>1</v>
@@ -5903,7 +5960,7 @@
         <v>1000</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="U100" s="1">
         <v>50036</v>
@@ -5914,7 +5971,7 @@
         <v>97</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
@@ -5926,7 +5983,7 @@
         <v>1000</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="U101" s="1">
         <v>50036</v>
@@ -5937,7 +5994,7 @@
         <v>98</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F102" s="1">
         <v>1</v>
@@ -5949,7 +6006,7 @@
         <v>1000</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="U102" s="1">
         <v>50036</v>
@@ -5960,7 +6017,7 @@
         <v>99</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F103" s="1">
         <v>1</v>
@@ -5972,7 +6029,7 @@
         <v>1000</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U103" s="1">
         <v>50036</v>
@@ -5983,7 +6040,7 @@
         <v>100</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F104" s="1">
         <v>1</v>
@@ -5995,7 +6052,7 @@
         <v>1000</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="U104" s="1">
         <v>50036</v>
@@ -6006,7 +6063,7 @@
         <v>101</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F105" s="1">
         <v>1</v>
@@ -6018,7 +6075,7 @@
         <v>1000</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U105" s="1">
         <v>50036</v>
@@ -6029,7 +6086,7 @@
         <v>102</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F106" s="1">
         <v>1</v>
@@ -6041,7 +6098,7 @@
         <v>1000</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U106" s="1">
         <v>50036</v>
@@ -6052,7 +6109,7 @@
         <v>103</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F107" s="1">
         <v>1</v>
@@ -6064,7 +6121,7 @@
         <v>1000</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U107" s="1">
         <v>50036</v>
@@ -6075,7 +6132,7 @@
         <v>104</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C108" s="1">
         <v>44</v>
@@ -6090,10 +6147,10 @@
         <v>1000</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="U108" s="1">
         <v>50036</v>
@@ -6104,7 +6161,7 @@
         <v>105</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C109" s="1">
         <v>44</v>
@@ -6119,10 +6176,10 @@
         <v>1000</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="U109" s="1">
         <v>50036</v>
@@ -6133,7 +6190,7 @@
         <v>106</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C110" s="1">
         <v>44</v>
@@ -6148,10 +6205,10 @@
         <v>1000</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="U110" s="1">
         <v>50036</v>
@@ -6162,7 +6219,7 @@
         <v>107</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C111" s="1">
         <v>44</v>
@@ -6177,7 +6234,7 @@
         <v>1000</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="U111" s="1">
         <v>50036</v>
@@ -6188,7 +6245,7 @@
         <v>108</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C112" s="1">
         <v>44</v>
@@ -6203,7 +6260,7 @@
         <v>1000</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U112" s="1">
         <v>50036</v>
@@ -6214,7 +6271,7 @@
         <v>109</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C113" s="1">
         <v>44</v>
@@ -6229,7 +6286,7 @@
         <v>1000</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U113" s="1">
         <v>50036</v>
@@ -6240,7 +6297,7 @@
         <v>110</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C114" s="1">
         <v>44</v>
@@ -6255,7 +6312,7 @@
         <v>1000</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U114" s="1">
         <v>50036</v>
@@ -6266,7 +6323,7 @@
         <v>111</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C115" s="1">
         <v>44</v>
@@ -6281,7 +6338,7 @@
         <v>1000</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="U115" s="1">
         <v>50036</v>
@@ -6292,7 +6349,7 @@
         <v>112</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C116" s="1">
         <v>44</v>
@@ -6307,7 +6364,7 @@
         <v>1000</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="U116" s="1">
         <v>50036</v>
@@ -6318,7 +6375,7 @@
         <v>113</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C117" s="1">
         <v>44</v>
@@ -6333,7 +6390,7 @@
         <v>1000</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U117" s="1">
         <v>50036</v>
@@ -6344,7 +6401,7 @@
         <v>114</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C118" s="1">
         <v>44</v>
@@ -6359,7 +6416,7 @@
         <v>1000</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="U118" s="1">
         <v>50036</v>
@@ -6370,7 +6427,7 @@
         <v>115</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C119" s="1">
         <v>44</v>
@@ -6385,7 +6442,7 @@
         <v>1000</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U119" s="1">
         <v>50036</v>
@@ -6396,7 +6453,7 @@
         <v>116</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
@@ -6419,7 +6476,7 @@
         <v>117</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F121" s="1">
         <v>1</v>
@@ -6442,7 +6499,7 @@
         <v>118</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F122" s="1">
         <v>1</v>
@@ -6465,7 +6522,7 @@
         <v>119</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
@@ -6488,7 +6545,7 @@
         <v>120</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
@@ -6511,7 +6568,7 @@
         <v>121</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
@@ -6534,7 +6591,7 @@
         <v>122</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
@@ -6557,7 +6614,7 @@
         <v>123</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C127" s="1">
         <v>91</v>
@@ -6583,7 +6640,7 @@
         <v>124</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
@@ -6606,7 +6663,7 @@
         <v>125</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F129" s="1">
         <v>1</v>
@@ -6629,7 +6686,7 @@
         <v>126</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C130" s="1">
         <v>44</v>
@@ -6644,7 +6701,7 @@
         <v>1000</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="U130" s="1">
         <v>50036</v>
@@ -6655,10 +6712,10 @@
         <v>127</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="U131" s="1">
         <v>50051</v>
@@ -6669,7 +6726,7 @@
         <v>128</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C132" s="1">
         <v>102</v>
@@ -6681,7 +6738,7 @@
         <v>800</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="U132" s="1">
         <v>100065</v>
@@ -6692,7 +6749,7 @@
         <v>129</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C133" s="1">
         <v>104</v>
@@ -6706,7 +6763,7 @@
         <v>130</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M134" s="1">
         <v>1</v>
@@ -6726,7 +6783,7 @@
         <v>131</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C135" s="1">
         <v>107</v>
@@ -6740,10 +6797,10 @@
         <v>132</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E136" s="1">
         <v>200</v>
@@ -6760,7 +6817,7 @@
         <v>133</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C137" s="1">
         <v>120</v>
@@ -6780,7 +6837,7 @@
         <v>134</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C138" s="1">
         <v>119</v>
@@ -6794,7 +6851,7 @@
         <v>135</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C139" s="1">
         <v>122</v>
@@ -6806,13 +6863,13 @@
         <v>1</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q139" s="1">
         <v>1</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S139" s="1">
         <v>1</v>
@@ -6826,10 +6883,10 @@
         <v>136</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U140" s="1">
         <v>50040</v>
@@ -6840,7 +6897,7 @@
         <v>137</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F141" s="1">
         <v>1</v>
@@ -6863,7 +6920,7 @@
         <v>138</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F142" s="1">
         <v>1</v>
@@ -6886,7 +6943,7 @@
         <v>139</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F143" s="1">
         <v>1</v>
@@ -6909,7 +6966,7 @@
         <v>140</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F144" s="1">
         <v>1</v>
@@ -6932,7 +6989,7 @@
         <v>141</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F145" s="1">
         <v>1</v>
@@ -6955,7 +7012,7 @@
         <v>142</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F146" s="1">
         <v>1</v>
@@ -6978,7 +7035,7 @@
         <v>143</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F147" s="1">
         <v>1</v>
@@ -6990,10 +7047,10 @@
         <v>1000</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U147" s="1">
         <v>50035</v>
@@ -7004,7 +7061,7 @@
         <v>144</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F148" s="1">
         <v>1</v>
@@ -7016,10 +7073,10 @@
         <v>1000</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U148" s="1">
         <v>50035</v>
@@ -7030,7 +7087,7 @@
         <v>145</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F149" s="1">
         <v>1</v>
@@ -7042,10 +7099,10 @@
         <v>1000</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U149" s="1">
         <v>50035</v>
@@ -7056,7 +7113,7 @@
         <v>146</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F150" s="1">
         <v>1</v>
@@ -7068,7 +7125,7 @@
         <v>1000</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="U150" s="1">
         <v>50035</v>
@@ -7079,10 +7136,10 @@
         <v>147</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F151" s="1">
         <v>1</v>
@@ -7094,7 +7151,7 @@
         <v>1000</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="U151" s="1">
         <v>50039</v>
@@ -7105,10 +7162,10 @@
         <v>148</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F152" s="1">
         <v>1</v>
@@ -7120,7 +7177,7 @@
         <v>1000</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="U152" s="1">
         <v>50039</v>
@@ -7131,10 +7188,10 @@
         <v>149</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F153" s="1">
         <v>1</v>
@@ -7146,7 +7203,7 @@
         <v>1000</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="U153" s="1">
         <v>50039</v>
@@ -7157,10 +7214,10 @@
         <v>150</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F154" s="1">
         <v>1</v>
@@ -7172,7 +7229,7 @@
         <v>1000</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U154" s="1">
         <v>50039</v>
@@ -7183,10 +7240,10 @@
         <v>151</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F155" s="1">
         <v>1</v>
@@ -7198,7 +7255,7 @@
         <v>1000</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="U155" s="1">
         <v>50039</v>
@@ -7209,10 +7266,10 @@
         <v>152</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F156" s="1">
         <v>1</v>
@@ -7224,7 +7281,7 @@
         <v>1000</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="U156" s="1">
         <v>50039</v>
@@ -7235,7 +7292,7 @@
         <v>153</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F157" s="1">
         <v>1</v>
@@ -7279,7 +7336,7 @@
         <v>154</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F158" s="1">
         <v>1</v>
@@ -7323,7 +7380,7 @@
         <v>155</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F159" s="1">
         <v>1</v>
@@ -7367,7 +7424,7 @@
         <v>156</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F160" s="1">
         <v>1</v>
@@ -7411,7 +7468,7 @@
         <v>157</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F161" s="1">
         <v>1</v>
@@ -7455,7 +7512,7 @@
         <v>158</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F162" s="1">
         <v>1</v>
@@ -7499,7 +7556,7 @@
         <v>159</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C163" s="1">
         <v>35</v>
@@ -7511,10 +7568,10 @@
         <v>1000</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U163" s="1">
         <v>50038</v>
@@ -7525,7 +7582,7 @@
         <v>160</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C164" s="1">
         <v>35</v>
@@ -7537,10 +7594,10 @@
         <v>1000</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U164" s="1">
         <v>50038</v>
@@ -7551,7 +7608,7 @@
         <v>161</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C165" s="1">
         <v>35</v>
@@ -7563,10 +7620,10 @@
         <v>1000</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K165" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U165" s="1">
         <v>50038</v>
@@ -7577,7 +7634,7 @@
         <v>162</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C166" s="1">
         <v>35</v>
@@ -7589,10 +7646,10 @@
         <v>1000</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K166" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U166" s="1">
         <v>50038</v>
@@ -7603,7 +7660,7 @@
         <v>163</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C167" s="1">
         <v>35</v>
@@ -7615,10 +7672,10 @@
         <v>1000</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U167" s="1">
         <v>50038</v>
@@ -7629,7 +7686,7 @@
         <v>164</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C168" s="1">
         <v>35</v>
@@ -7641,10 +7698,10 @@
         <v>1000</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U168" s="1">
         <v>50038</v>
@@ -7655,7 +7712,7 @@
         <v>165</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F169" s="1">
         <v>1</v>
@@ -7699,7 +7756,7 @@
         <v>166</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C170" s="1">
         <v>145</v>
@@ -7711,7 +7768,7 @@
         <v>1000</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M170" s="1">
         <v>1</v>
@@ -7743,7 +7800,7 @@
         <v>167</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C171" s="1">
         <v>145</v>
@@ -7755,7 +7812,7 @@
         <v>1000</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M171" s="1">
         <v>1</v>
@@ -7787,7 +7844,7 @@
         <v>168</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C172" s="1">
         <v>145</v>
@@ -7799,7 +7856,7 @@
         <v>1000</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M172" s="1">
         <v>1</v>
@@ -7831,7 +7888,7 @@
         <v>169</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C173" s="1">
         <v>145</v>
@@ -7843,7 +7900,7 @@
         <v>1000</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M173" s="1">
         <v>1</v>
@@ -7875,7 +7932,7 @@
         <v>170</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C174" s="1">
         <v>145</v>
@@ -7887,7 +7944,7 @@
         <v>1000</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M174" s="1">
         <v>1</v>
@@ -7919,7 +7976,7 @@
         <v>171</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C175" s="1">
         <v>145</v>
@@ -7931,7 +7988,7 @@
         <v>1000</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M175" s="1">
         <v>1</v>
@@ -7963,7 +8020,7 @@
         <v>172</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C176" s="1">
         <v>145</v>
@@ -7975,7 +8032,7 @@
         <v>1000</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M176" s="1">
         <v>1</v>
@@ -8007,7 +8064,7 @@
         <v>173</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C177" s="1">
         <v>145</v>
@@ -8019,7 +8076,7 @@
         <v>1000</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M177" s="1">
         <v>1</v>
@@ -8051,7 +8108,7 @@
         <v>174</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C178" s="1">
         <v>145</v>
@@ -8063,7 +8120,7 @@
         <v>1000</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M178" s="1">
         <v>1</v>
@@ -8095,7 +8152,7 @@
         <v>175</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C179" s="1">
         <v>145</v>
@@ -8107,7 +8164,7 @@
         <v>1000</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M179" s="1">
         <v>1</v>
@@ -8139,7 +8196,7 @@
         <v>176</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C180" s="1">
         <v>145</v>
@@ -8151,7 +8208,7 @@
         <v>1000</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M180" s="1">
         <v>1</v>
@@ -8183,7 +8240,7 @@
         <v>177</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C181" s="1">
         <v>145</v>
@@ -8195,7 +8252,7 @@
         <v>1000</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M181" s="1">
         <v>1</v>
@@ -8227,7 +8284,7 @@
         <v>178</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C182" s="1">
         <v>145</v>
@@ -8239,7 +8296,7 @@
         <v>1000</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M182" s="1">
         <v>1</v>
@@ -8271,7 +8328,7 @@
         <v>179</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C183" s="1">
         <v>145</v>
@@ -8283,7 +8340,7 @@
         <v>1000</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M183" s="1">
         <v>1</v>
@@ -8315,7 +8372,7 @@
         <v>180</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C184" s="1">
         <v>145</v>
@@ -8327,7 +8384,7 @@
         <v>1000</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M184" s="1">
         <v>1</v>
@@ -8359,7 +8416,7 @@
         <v>181</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C185" s="1">
         <v>145</v>
@@ -8371,7 +8428,7 @@
         <v>1000</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M185" s="1">
         <v>1</v>
@@ -8403,7 +8460,7 @@
         <v>182</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C186" s="1">
         <v>145</v>
@@ -8415,7 +8472,7 @@
         <v>1000</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M186" s="1">
         <v>1</v>
@@ -8447,7 +8504,7 @@
         <v>183</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C187" s="1">
         <v>145</v>
@@ -8459,7 +8516,7 @@
         <v>1000</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M187" s="1">
         <v>1</v>
@@ -8491,7 +8548,7 @@
         <v>184</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C188" s="1">
         <v>145</v>
@@ -8503,7 +8560,7 @@
         <v>1000</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M188" s="1">
         <v>1</v>
@@ -8535,7 +8592,7 @@
         <v>185</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C189" s="1">
         <v>126</v>
@@ -8547,7 +8604,7 @@
         <v>1000</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="U189" s="1">
         <v>50038</v>
@@ -8558,7 +8615,7 @@
         <v>186</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C190" s="1">
         <v>126</v>
@@ -8570,10 +8627,10 @@
         <v>1000</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U190" s="1">
         <v>50038</v>
@@ -8584,7 +8641,7 @@
         <v>187</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C191" s="1">
         <v>126</v>
@@ -8596,10 +8653,10 @@
         <v>1000</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U191" s="1">
         <v>50038</v>
@@ -8610,7 +8667,7 @@
         <v>188</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C192" s="1">
         <v>126</v>
@@ -8622,10 +8679,10 @@
         <v>1000</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U192" s="1">
         <v>50038</v>
@@ -8636,7 +8693,7 @@
         <v>189</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C193" s="1">
         <v>126</v>
@@ -8648,10 +8705,10 @@
         <v>1000</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U193" s="1">
         <v>50038</v>
@@ -8662,7 +8719,7 @@
         <v>190</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C194" s="1">
         <v>126</v>
@@ -8674,10 +8731,10 @@
         <v>1000</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U194" s="1">
         <v>50038</v>
@@ -8688,7 +8745,7 @@
         <v>191</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C195" s="1">
         <v>126</v>
@@ -8700,10 +8757,10 @@
         <v>1000</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K195" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U195" s="1">
         <v>50038</v>
@@ -8714,7 +8771,7 @@
         <v>192</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C196" s="1">
         <v>126</v>
@@ -8726,10 +8783,10 @@
         <v>1000</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K196" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U196" s="1">
         <v>50038</v>
@@ -8740,7 +8797,7 @@
         <v>193</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C197" s="1">
         <v>126</v>
@@ -8752,10 +8809,10 @@
         <v>1000</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U197" s="1">
         <v>50038</v>
@@ -8766,7 +8823,7 @@
         <v>194</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C198" s="1">
         <v>126</v>
@@ -8778,10 +8835,10 @@
         <v>1000</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U198" s="1">
         <v>50038</v>
@@ -8792,7 +8849,7 @@
         <v>195</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C199" s="1">
         <v>126</v>
@@ -8804,10 +8861,10 @@
         <v>1000</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K199" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U199" s="1">
         <v>50038</v>
@@ -8818,7 +8875,7 @@
         <v>196</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C200" s="1">
         <v>126</v>
@@ -8830,7 +8887,7 @@
         <v>1000</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="U200" s="1">
         <v>50038</v>
@@ -8841,7 +8898,7 @@
         <v>197</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C201" s="1">
         <v>126</v>
@@ -8853,7 +8910,7 @@
         <v>1000</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="U201" s="1">
         <v>50038</v>
@@ -8864,7 +8921,7 @@
         <v>198</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C202" s="1">
         <v>126</v>
@@ -8876,7 +8933,7 @@
         <v>1000</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="U202" s="1">
         <v>50038</v>
@@ -8887,7 +8944,7 @@
         <v>199</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C203" s="1">
         <v>126</v>
@@ -8899,7 +8956,7 @@
         <v>1000</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="U203" s="1">
         <v>50038</v>
@@ -8910,7 +8967,7 @@
         <v>200</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C204" s="1">
         <v>126</v>
@@ -8922,7 +8979,7 @@
         <v>1000</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="U204" s="1">
         <v>50038</v>
@@ -8933,7 +8990,7 @@
         <v>201</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C205" s="1">
         <v>126</v>
@@ -8945,7 +9002,7 @@
         <v>1000</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U205" s="1">
         <v>50038</v>
@@ -8956,7 +9013,7 @@
         <v>202</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C206" s="1">
         <v>126</v>
@@ -8968,7 +9025,7 @@
         <v>1000</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="U206" s="1">
         <v>50038</v>
@@ -8979,7 +9036,7 @@
         <v>203</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C207" s="1">
         <v>126</v>
@@ -8991,7 +9048,7 @@
         <v>1000</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="U207" s="1">
         <v>50038</v>
@@ -9002,10 +9059,10 @@
         <v>204</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F208" s="1">
         <v>1</v>
@@ -9014,10 +9071,10 @@
         <v>1000</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U208" s="1">
         <v>50039</v>
@@ -9028,22 +9085,22 @@
         <v>205</v>
       </c>
       <c r="B209" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F209" s="1">
+        <v>1</v>
+      </c>
+      <c r="H209" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J209" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="F209" s="1">
-        <v>1</v>
-      </c>
-      <c r="H209" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I209" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="J209" s="1" t="s">
-        <v>394</v>
       </c>
       <c r="U209" s="1">
         <v>50039</v>
@@ -9054,10 +9111,10 @@
         <v>206</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F210" s="1">
         <v>1</v>
@@ -9066,10 +9123,10 @@
         <v>1000</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U210" s="1">
         <v>50039</v>
@@ -9080,10 +9137,10 @@
         <v>207</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F211" s="1">
         <v>1</v>
@@ -9092,10 +9149,10 @@
         <v>1000</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U211" s="1">
         <v>50039</v>
@@ -9106,10 +9163,10 @@
         <v>208</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F212" s="1">
         <v>1</v>
@@ -9118,10 +9175,10 @@
         <v>1000</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U212" s="1">
         <v>50039</v>
@@ -9132,10 +9189,10 @@
         <v>209</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F213" s="1">
         <v>1</v>
@@ -9144,10 +9201,10 @@
         <v>1000</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U213" s="1">
         <v>50039</v>
@@ -9158,10 +9215,10 @@
         <v>210</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F214" s="1">
         <v>1</v>
@@ -9170,10 +9227,10 @@
         <v>1000</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U214" s="1">
         <v>50039</v>
@@ -9184,10 +9241,10 @@
         <v>211</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F215" s="1">
         <v>1</v>
@@ -9196,10 +9253,10 @@
         <v>1000</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U215" s="1">
         <v>50039</v>
@@ -9210,10 +9267,10 @@
         <v>212</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F216" s="1">
         <v>1</v>
@@ -9222,10 +9279,10 @@
         <v>1000</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U216" s="1">
         <v>50039</v>
@@ -9236,10 +9293,10 @@
         <v>213</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F217" s="1">
         <v>1</v>
@@ -9248,10 +9305,10 @@
         <v>1000</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U217" s="1">
         <v>50039</v>
@@ -9262,10 +9319,10 @@
         <v>214</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F218" s="1">
         <v>1</v>
@@ -9274,10 +9331,10 @@
         <v>1000</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J218" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U218" s="1">
         <v>50039</v>
@@ -9288,10 +9345,10 @@
         <v>215</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F219" s="1">
         <v>1</v>
@@ -9300,10 +9357,10 @@
         <v>1000</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U219" s="1">
         <v>50039</v>
@@ -9314,10 +9371,10 @@
         <v>216</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F220" s="1">
         <v>1</v>
@@ -9326,10 +9383,10 @@
         <v>1000</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U220" s="1">
         <v>50039</v>
@@ -9340,10 +9397,10 @@
         <v>217</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F221" s="1">
         <v>1</v>
@@ -9352,10 +9409,10 @@
         <v>1000</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U221" s="1">
         <v>50039</v>
@@ -9366,10 +9423,10 @@
         <v>218</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F222" s="1">
         <v>1</v>
@@ -9378,10 +9435,10 @@
         <v>1000</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U222" s="1">
         <v>50039</v>
@@ -9392,10 +9449,10 @@
         <v>219</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F223" s="1">
         <v>1</v>
@@ -9404,10 +9461,10 @@
         <v>1000</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U223" s="1">
         <v>50039</v>
@@ -9418,10 +9475,10 @@
         <v>220</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F224" s="1">
         <v>1</v>
@@ -9430,10 +9487,10 @@
         <v>1000</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U224" s="1">
         <v>50039</v>
@@ -9444,10 +9501,10 @@
         <v>221</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F225" s="1">
         <v>1</v>
@@ -9456,10 +9513,10 @@
         <v>1000</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U225" s="1">
         <v>50039</v>
@@ -9470,10 +9527,10 @@
         <v>222</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F226" s="1">
         <v>1</v>
@@ -9482,10 +9539,10 @@
         <v>1000</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U226" s="1">
         <v>50039</v>
@@ -9496,10 +9553,10 @@
         <v>223</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F227" s="1">
         <v>1</v>
@@ -9508,10 +9565,10 @@
         <v>1000</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U227" s="1">
         <v>50039</v>
@@ -9522,10 +9579,10 @@
         <v>224</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="U228" s="1">
         <v>50011</v>
@@ -9536,7 +9593,7 @@
         <v>225</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C229" s="1">
         <v>130</v>
@@ -9559,13 +9616,13 @@
         <v>226</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U230" s="1">
         <v>50014</v>
@@ -9576,10 +9633,10 @@
         <v>227</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M231" s="1">
         <v>1</v>
@@ -9605,16 +9662,16 @@
         <v>228</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M232" s="1">
         <v>1</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P232" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q232" s="1">
         <v>2</v>
@@ -9628,7 +9685,7 @@
         <v>229</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M233" s="1">
         <v>1</v>
@@ -9648,10 +9705,10 @@
         <v>230</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="U234" s="1">
         <v>50052</v>
@@ -9662,7 +9719,7 @@
         <v>231</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C235" s="1">
         <v>139</v>
@@ -9676,10 +9733,10 @@
         <v>232</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="U236" s="1">
         <v>50051</v>
@@ -9690,7 +9747,7 @@
         <v>233</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C237" s="1">
         <v>126</v>
@@ -9702,7 +9759,7 @@
         <v>1000</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="U237" s="1">
         <v>50038</v>
@@ -9713,7 +9770,7 @@
         <v>234</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C238" s="1">
         <v>145</v>
@@ -9725,7 +9782,7 @@
         <v>1000</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M238" s="1">
         <v>1</v>
@@ -9757,7 +9814,7 @@
         <v>1001</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F239" s="1">
         <v>1</v>
@@ -9786,7 +9843,7 @@
         <v>1002</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F240" s="1">
         <v>1</v>
@@ -9815,7 +9872,7 @@
         <v>1004</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C241" s="1">
         <v>1004</v>
@@ -9838,7 +9895,7 @@
         <v>1005</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F242" s="1">
         <v>1</v>
@@ -9858,7 +9915,7 @@
         <v>1006</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F243" s="1">
         <v>1</v>
@@ -9875,7 +9932,7 @@
         <v>1007</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M244" s="1">
         <v>1</v>
@@ -9895,7 +9952,7 @@
         <v>1009</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C245" s="1">
         <v>1009</v>
@@ -9909,7 +9966,7 @@
         <v>1010</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H246" s="1">
         <v>1000</v>
@@ -9926,7 +9983,7 @@
         <v>1011</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C247" s="1">
         <v>1011</v>
@@ -9940,7 +9997,7 @@
         <v>1012</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C248" s="1">
         <v>2011</v>
@@ -9966,7 +10023,7 @@
         <v>1014</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C249" s="1">
         <v>1014</v>
@@ -9980,7 +10037,7 @@
         <v>1015</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C250" s="1">
         <v>1015</v>
@@ -9994,7 +10051,7 @@
         <v>1016</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C251" s="1">
         <v>1016</v>
@@ -10008,7 +10065,7 @@
         <v>1017</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F252" s="1">
         <v>1</v>
@@ -10025,7 +10082,7 @@
         <v>1018</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C253" s="1">
         <v>2024</v>
@@ -10039,7 +10096,7 @@
         <v>1021</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F254" s="1">
         <v>1</v>
@@ -10059,13 +10116,13 @@
         <v>1022</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="256" spans="1:17">
@@ -10073,7 +10130,7 @@
         <v>1023</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M256" s="1">
         <v>1</v>
@@ -10096,7 +10153,7 @@
         <v>1024</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M257" s="1">
         <v>1</v>
@@ -10119,7 +10176,7 @@
         <v>1025</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C258" s="1">
         <v>1022</v>
@@ -10133,7 +10190,7 @@
         <v>1026</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C259" s="1">
         <v>1023</v>
@@ -10147,7 +10204,7 @@
         <v>1027</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C260" s="1">
         <v>1024</v>
@@ -10185,7 +10242,7 @@
         <v>1028</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M261" s="1">
         <v>1</v>
@@ -10208,7 +10265,7 @@
         <v>1029</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C262" s="1">
         <v>1028</v>
@@ -10222,7 +10279,7 @@
         <v>2001</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C263" s="1">
         <v>2001</v>
@@ -10233,7 +10290,7 @@
         <v>2002</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F264" s="1">
         <v>1</v>
@@ -10250,7 +10307,7 @@
         <v>2003</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M265" s="1">
         <v>1</v>
@@ -10264,7 +10321,7 @@
         <v>2004</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F266" s="1">
         <v>1</v>
@@ -10284,7 +10341,7 @@
         <v>2005</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C267" s="1">
         <v>2006</v>
@@ -10304,7 +10361,7 @@
         <v>2006</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C268" s="1">
         <v>2007</v>
@@ -10318,7 +10375,7 @@
         <v>2007</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F269" s="1">
         <v>1</v>
@@ -10327,7 +10384,7 @@
         <v>1000</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="270" spans="1:17">
@@ -10335,7 +10392,7 @@
         <v>2008</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C270" s="1">
         <v>2009</v>
@@ -10349,7 +10406,7 @@
         <v>2009</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C271" s="1">
         <v>2010</v>
@@ -10360,7 +10417,7 @@
         <v>2010</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C272" s="1">
         <v>2011</v>
@@ -10380,7 +10437,7 @@
         <v>2011</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C273" s="1">
         <v>2012</v>
@@ -10391,7 +10448,7 @@
         <v>2012</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C274" s="1">
         <v>2013</v>
@@ -10405,7 +10462,7 @@
         <v>2013</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C275" s="1">
         <v>2014</v>
@@ -10416,7 +10473,7 @@
         <v>2014</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C276" s="1">
         <v>2015</v>
@@ -10436,7 +10493,7 @@
         <v>2015</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C277" s="1">
         <v>2016</v>
@@ -10447,7 +10504,7 @@
         <v>2016</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C278" s="1">
         <v>2017</v>
@@ -10467,7 +10524,7 @@
         <v>2017</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C279" s="1">
         <v>2018</v>
@@ -10481,7 +10538,7 @@
         <v>2018</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C280" s="1">
         <v>2020</v>
@@ -10492,7 +10549,7 @@
         <v>2019</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C281" s="1">
         <v>2021</v>
@@ -10512,7 +10569,7 @@
         <v>2020</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C282" s="1">
         <v>2022</v>
@@ -10532,7 +10589,7 @@
         <v>2021</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C283" s="1">
         <v>2023</v>
@@ -10552,7 +10609,7 @@
         <v>2022</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C284" s="1">
         <v>2024</v>
@@ -10563,7 +10620,7 @@
         <v>2023</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C285" s="1">
         <v>2025</v>
@@ -10583,10 +10640,10 @@
         <v>2024</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M286" s="1">
         <v>1</v>
@@ -10603,7 +10660,7 @@
         <v>2025</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="288" spans="1:17">
@@ -10611,10 +10668,10 @@
         <v>2026</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F288" s="1">
         <v>1</v>
@@ -10628,7 +10685,7 @@
         <v>2027</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C289" s="1">
         <v>19</v>
@@ -10648,7 +10705,7 @@
         <v>2028</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="291" spans="1:20">
@@ -10656,10 +10713,10 @@
         <v>2029</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M291" s="1">
         <v>1</v>
@@ -10670,7 +10727,7 @@
         <v>2030</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F292" s="1">
         <v>1</v>
@@ -10690,7 +10747,7 @@
         <v>3001</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C293" s="1">
         <v>3001</v>
@@ -10704,7 +10761,7 @@
         <v>3002</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C294" s="1">
         <v>3002</v>
@@ -10718,7 +10775,7 @@
         <v>3003</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C295" s="1">
         <v>3003</v>
@@ -10732,7 +10789,7 @@
         <v>4000</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C296" s="1">
         <v>4000</v>
@@ -10746,7 +10803,7 @@
         <v>4010</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C297" s="1">
         <v>4010</v>
@@ -10760,7 +10817,7 @@
         <v>4020</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C298" s="1">
         <v>4020</v>
@@ -10771,7 +10828,7 @@
         <v>4030</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C299" s="1">
         <v>4030</v>
@@ -10782,7 +10839,7 @@
         <v>4040</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C300" s="1">
         <v>4040</v>
@@ -10802,7 +10859,7 @@
         <v>4050</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C301" s="1">
         <v>4050</v>
@@ -10834,7 +10891,7 @@
         <v>4060</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C302" s="1">
         <v>4060</v>
@@ -10845,7 +10902,7 @@
         <v>4070</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C303" s="1">
         <v>4070</v>
@@ -10857,7 +10914,7 @@
         <v>1000</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="304" spans="1:20">
@@ -10865,7 +10922,7 @@
         <v>4080</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C304" s="1">
         <v>4080</v>
@@ -10885,7 +10942,7 @@
         <v>4090</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C305" s="1">
         <v>4090</v>
@@ -10899,7 +10956,7 @@
         <v>4100</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C306" s="1">
         <v>4100</v>
@@ -10919,7 +10976,7 @@
         <v>4110</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C307" s="1">
         <v>4110</v>
@@ -10930,7 +10987,7 @@
         <v>4112</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C308" s="1">
         <v>4112</v>
@@ -10941,13 +10998,13 @@
         <v>6000</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C309" s="1">
         <v>6000</v>
       </c>
-      <c r="D309" s="1" t="s">
-        <v>510</v>
+      <c r="D309" s="1">
+        <v>1</v>
       </c>
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
@@ -11606,10 +11663,10 @@
         <v>561</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="348" spans="1:21">
@@ -11786,7 +11843,7 @@
         <v>1</v>
       </c>
       <c r="U355" s="1">
-        <v>50023</v>
+        <v>50025</v>
       </c>
     </row>
     <row r="356" spans="1:21">
@@ -11806,7 +11863,7 @@
         <v>2</v>
       </c>
       <c r="U356" s="1">
-        <v>50023</v>
+        <v>50017</v>
       </c>
     </row>
     <row r="357" spans="1:21">
@@ -11829,7 +11886,7 @@
         <v>5</v>
       </c>
       <c r="U357" s="1">
-        <v>50023</v>
+        <v>50020</v>
       </c>
     </row>
     <row r="358" spans="1:21">
@@ -11857,25 +11914,25 @@
         <v>573</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E359" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="M359" s="1">
+        <v>1</v>
+      </c>
+      <c r="O359" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="M359" s="1">
-        <v>1</v>
-      </c>
-      <c r="O359" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="P359" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q359" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U359" s="1">
         <v>50018</v>
@@ -11889,7 +11946,7 @@
         <v>574</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D360" s="1">
         <v>1</v>
@@ -11944,7 +12001,7 @@
       <c r="S361" s="1"/>
       <c r="T361" s="1"/>
       <c r="U361" s="1">
-        <v>50012</v>
+        <v>50037</v>
       </c>
     </row>
   </sheetData>
